--- a/data/fullyear-resilience/Power_Storage.xlsx
+++ b/data/fullyear-resilience/Power_Storage.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\fullyear-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96C6AE4-695E-42EE-9969-B47103F81902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145B0F8A-17C0-4DC8-9055-634D1B07A432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
+    <sheet name="year2017" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{69136B6C-42D6-4ADF-8E3E-6F0F37636C5F}">
       <text>
         <r>
           <rPr>
@@ -52,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{E4F75161-4B98-49B9-B0D5-8EBD6813A429}">
       <text>
         <r>
           <rPr>
@@ -66,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{43729DAC-BC0B-4FF1-B7A2-D9CED32C93B0}">
       <text>
         <r>
           <rPr>
@@ -80,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{4F375068-B303-400C-AA70-059638CA72E6}">
       <text>
         <r>
           <rPr>
@@ -94,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{11DF428A-0E4D-40B0-B77E-22CE8D9453B3}">
       <text>
         <r>
           <rPr>
@@ -108,7 +109,101 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{75C1E1A6-FC03-43D8-8DAC-C8E8A32DADD5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Unit or valid values</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{539CD6F4-E0CC-49C7-BDEC-67A05C0E4FEF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>If a line has a value in this column, it is not read in (i.e., does not exist).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{2A1AF3D6-AC83-4E05-A1F3-B9E3FA7A02D7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Readable name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{68F54567-F86B-48D0-91DF-08372551F975}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Value specifier in database</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{64726565-7644-4D6B-A09B-5225E416160A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Description</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{0CDE00F7-099D-41D0-887A-DE2DE28F0AE7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Details on database behavior</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{5045AFC7-DBF5-4648-A3D3-C7AC9CCB6F69}">
       <text>
         <r>
           <rPr>
@@ -127,7 +222,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="99">
   <si>
     <t>Power - Storage</t>
   </si>
@@ -1430,9 +1525,11 @@
       <c r="N8" s="14">
         <v>0</v>
       </c>
-      <c r="O8" s="15"/>
+      <c r="O8" s="15">
+        <v>0</v>
+      </c>
       <c r="P8" s="15">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q8" s="13">
         <v>0</v>
@@ -1444,7 +1541,745 @@
         <v>1</v>
       </c>
       <c r="T8" s="13">
+        <v>50</v>
+      </c>
+      <c r="U8" s="15">
+        <v>3821.0756000000001</v>
+      </c>
+      <c r="V8" s="15">
+        <v>15584.302299999999</v>
+      </c>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
+      <c r="X8" s="16">
+        <v>0.96</v>
+      </c>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="17">
+        <v>46.77</v>
+      </c>
+      <c r="AB8" s="17">
+        <v>13.746700000000001</v>
+      </c>
+      <c r="AC8" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD8" s="18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="18"/>
+      <c r="AD9" s="18"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="18"/>
+      <c r="AD10" s="18"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="18"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4F1348-9707-42FC-B0CD-EC35F03BF181}">
+  <sheetPr>
+    <tabColor rgb="FF008080"/>
+  </sheetPr>
+  <dimension ref="A1:AD12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="11" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="13" max="16" width="15.7109375" customWidth="1"/>
+    <col min="17" max="17" width="20.7109375" customWidth="1"/>
+    <col min="18" max="20" width="15.7109375" customWidth="1"/>
+    <col min="21" max="22" width="20.7109375" customWidth="1"/>
+    <col min="23" max="23" width="22.7109375" customWidth="1"/>
+    <col min="24" max="24" width="15.7109375" customWidth="1"/>
+    <col min="25" max="26" width="20.140625" customWidth="1"/>
+    <col min="27" max="28" width="15.7109375" customWidth="1"/>
+    <col min="29" max="30" width="24.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>10</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD3" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD4" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD5" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="T6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="X6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD6" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="W7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA7" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB7" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC7" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD7" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14">
+        <v>1</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0.95</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0.95</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0.03</v>
+      </c>
+      <c r="M8" s="14">
+        <v>0</v>
+      </c>
+      <c r="N8" s="14">
+        <v>0</v>
+      </c>
+      <c r="O8" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="P8" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+      <c r="R8" s="15">
+        <v>4</v>
+      </c>
+      <c r="S8" s="13">
+        <v>1</v>
+      </c>
+      <c r="T8" s="13">
+        <v>50</v>
       </c>
       <c r="U8" s="15">
         <v>3821.0756000000001</v>

--- a/data/fullyear-resilience/Power_Storage.xlsx
+++ b/data/fullyear-resilience/Power_Storage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\fullyear-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145B0F8A-17C0-4DC8-9055-634D1B07A432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CCCE12-8347-45CA-A6CD-095813AC28D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -1517,7 +1517,7 @@
         <v>0.95</v>
       </c>
       <c r="L8" s="15">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M8" s="14">
         <v>0</v>
@@ -1547,13 +1547,13 @@
         <v>3821.0756000000001</v>
       </c>
       <c r="V8" s="15">
-        <v>15584.302299999999</v>
+        <v>155804.30230000001</v>
       </c>
       <c r="W8" s="14">
         <v>4</v>
       </c>
       <c r="X8" s="16">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="13"/>
       <c r="Z8" s="13"/>
@@ -1700,7 +1700,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2255,7 +2256,7 @@
         <v>0.95</v>
       </c>
       <c r="L8" s="15">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="M8" s="14">
         <v>0</v>
@@ -2264,10 +2265,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="15">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P8" s="15">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="13">
         <v>0</v>
@@ -2285,13 +2286,13 @@
         <v>3821.0756000000001</v>
       </c>
       <c r="V8" s="15">
-        <v>15584.302299999999</v>
+        <v>155840.30230000001</v>
       </c>
       <c r="W8" s="14">
         <v>4</v>
       </c>
       <c r="X8" s="16">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="13"/>
       <c r="Z8" s="13"/>
@@ -2438,6 +2439,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/fullyear-resilience/Power_Storage.xlsx
+++ b/data/fullyear-resilience/Power_Storage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\fullyear-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CCCE12-8347-45CA-A6CD-095813AC28D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA185D2-F73D-4E57-9178-88653FC414DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="15">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P8" s="15">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S8" s="13">
         <v>1</v>
@@ -2283,10 +2283,10 @@
         <v>50</v>
       </c>
       <c r="U8" s="15">
-        <v>3821.0756000000001</v>
+        <v>0</v>
       </c>
       <c r="V8" s="15">
-        <v>155840.30230000001</v>
+        <v>15000</v>
       </c>
       <c r="W8" s="14">
         <v>4</v>

--- a/data/fullyear-resilience/Power_Storage.xlsx
+++ b/data/fullyear-resilience/Power_Storage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\fullyear-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA185D2-F73D-4E57-9178-88653FC414DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9851FF4-7EE8-40D7-8076-FC72B424832D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -525,7 +525,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="8" formatCode="&quot;€&quot;\ #,##0.00;[Red]\-&quot;€&quot;\ #,##0.00"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -620,7 +621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -666,6 +667,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -972,25 +975,25 @@
     <tabColor rgb="FF008080"/>
   </sheetPr>
   <dimension ref="A1:AD12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
-    <col min="13" max="16" width="15.7109375" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" customWidth="1"/>
-    <col min="18" max="20" width="15.7109375" customWidth="1"/>
-    <col min="21" max="22" width="20.7109375" customWidth="1"/>
-    <col min="23" max="23" width="22.7109375" customWidth="1"/>
-    <col min="24" max="24" width="15.7109375" customWidth="1"/>
-    <col min="25" max="26" width="20.140625" customWidth="1"/>
-    <col min="27" max="28" width="15.7109375" customWidth="1"/>
-    <col min="29" max="30" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.59765625" customWidth="1"/>
+    <col min="2" max="2" width="19.73046875" customWidth="1"/>
+    <col min="3" max="9" width="15.73046875" customWidth="1"/>
+    <col min="10" max="11" width="21.73046875" customWidth="1"/>
+    <col min="12" max="12" width="20.73046875" customWidth="1"/>
+    <col min="13" max="16" width="15.73046875" customWidth="1"/>
+    <col min="17" max="17" width="20.73046875" customWidth="1"/>
+    <col min="18" max="20" width="15.73046875" customWidth="1"/>
+    <col min="21" max="22" width="20.73046875" customWidth="1"/>
+    <col min="23" max="23" width="22.73046875" customWidth="1"/>
+    <col min="24" max="24" width="15.73046875" customWidth="1"/>
+    <col min="25" max="26" width="20.1328125" customWidth="1"/>
+    <col min="27" max="28" width="15.73046875" customWidth="1"/>
+    <col min="29" max="30" width="24.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1024,7 +1027,7 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1032,7 +1035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1124,7 +1127,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
@@ -1216,7 +1219,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -1306,7 +1309,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
         <v>76</v>
@@ -1396,7 +1399,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
         <v>79</v>
@@ -1486,7 +1489,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
@@ -1570,7 +1573,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
@@ -1602,7 +1605,7 @@
       <c r="AC9" s="18"/>
       <c r="AD9" s="18"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
@@ -1634,7 +1637,7 @@
       <c r="AC10" s="18"/>
       <c r="AD10" s="18"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -1666,7 +1669,7 @@
       <c r="AC11" s="18"/>
       <c r="AD11" s="18"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -1710,26 +1713,26 @@
   <sheetPr>
     <tabColor rgb="FF008080"/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AD26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
-    <col min="13" max="16" width="15.7109375" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" customWidth="1"/>
-    <col min="18" max="20" width="15.7109375" customWidth="1"/>
-    <col min="21" max="22" width="20.7109375" customWidth="1"/>
-    <col min="23" max="23" width="22.7109375" customWidth="1"/>
-    <col min="24" max="24" width="15.7109375" customWidth="1"/>
-    <col min="25" max="26" width="20.140625" customWidth="1"/>
-    <col min="27" max="28" width="15.7109375" customWidth="1"/>
-    <col min="29" max="30" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.59765625" customWidth="1"/>
+    <col min="2" max="2" width="19.73046875" customWidth="1"/>
+    <col min="3" max="9" width="15.73046875" customWidth="1"/>
+    <col min="10" max="11" width="21.73046875" customWidth="1"/>
+    <col min="12" max="12" width="20.73046875" customWidth="1"/>
+    <col min="13" max="16" width="15.73046875" customWidth="1"/>
+    <col min="17" max="17" width="20.73046875" customWidth="1"/>
+    <col min="18" max="20" width="15.73046875" customWidth="1"/>
+    <col min="21" max="22" width="20.73046875" customWidth="1"/>
+    <col min="23" max="23" width="22.73046875" customWidth="1"/>
+    <col min="24" max="24" width="15.73046875" customWidth="1"/>
+    <col min="25" max="26" width="20.1328125" customWidth="1"/>
+    <col min="27" max="28" width="15.73046875" customWidth="1"/>
+    <col min="29" max="30" width="24.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1763,7 +1766,7 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1771,7 +1774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1863,7 +1866,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
@@ -1955,7 +1958,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -2045,7 +2048,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
         <v>76</v>
@@ -2135,7 +2138,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
         <v>79</v>
@@ -2225,7 +2228,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
@@ -2309,7 +2312,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
@@ -2341,7 +2344,7 @@
       <c r="AC9" s="18"/>
       <c r="AD9" s="18"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
@@ -2373,7 +2376,7 @@
       <c r="AC10" s="18"/>
       <c r="AD10" s="18"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -2405,7 +2408,7 @@
       <c r="AC11" s="18"/>
       <c r="AD11" s="18"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -2437,6 +2440,13 @@
       <c r="AC12" s="18"/>
       <c r="AD12" s="18"/>
     </row>
+    <row r="24" spans="20:22" x14ac:dyDescent="0.45">
+      <c r="T24" s="19"/>
+    </row>
+    <row r="26" spans="20:22" x14ac:dyDescent="0.45">
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
